--- a/education_forms/048_mathematics_assessment_logarithms--education_forms.xlsx
+++ b/education_forms/048_mathematics_assessment_logarithms--education_forms.xlsx
@@ -1,15 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -43,12 +42,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,12 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -437,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -528,7 +518,11 @@
           <t>Page One</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Instructions - This is the first page of the assessment.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,7 +537,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page_two</t>
+          <t>student_information</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -551,7 +545,11 @@
           <t>Student Information</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Provide your name, email, and student ID.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,23 +559,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>logarithm_type</t>
+          <t>question_one</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Logarithm Type</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What is the value of log 2?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Use the correct base 10 logarithm.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,22 +591,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>question_two</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>What is the value of log (3/2) / 2?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Enter the answer</t>
+          <t>Simplify your answer.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -616,15 +618,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page_three</t>
+          <t>page_two</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Page Three</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Page Two</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>This is the second page of the assessment.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -639,18 +645,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>question_three</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is the value of log 2?</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is the value of log 3^2?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Use the correct base 10 logarithm.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -662,22 +672,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>question_four</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>What is the value of log 2 + 3?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Enter the answer</t>
+          <t>Simplify your answer.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -689,15 +699,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>page_four</t>
+          <t>page_three</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Page Four</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Page Three</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>This is the third page of the assessment.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -712,18 +726,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>question_five</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is the value of log (3/2) / 2?</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is the value of log (3/4) / 2?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Use the correct base 10 logarithm.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -735,22 +753,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>question_six</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>What is the value of log 0?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Enter the answer</t>
+          <t>This should be an undefined value.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -762,15 +780,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>page_five</t>
+          <t>page_four</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Page Five</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Page Four</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>This is the fourth page of the assessment.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -785,18 +807,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>question_seven</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is the value of log 3^2?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is the value of log (-1) / 4?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>This should be an undefined value.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -808,22 +834,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>question_eight</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>What is the value of log 2 - 1?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Enter the answer</t>
+          <t>Simplify your answer.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -835,18 +861,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>page_six</t>
+          <t>question_nine</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Page Six</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>What is the value of log 2^2 + 2?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Use the correct base 10 logarithm.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -858,18 +888,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>question_ten</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What is the value of log (3/4) / 2?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>What is the value of log 2 - 2?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>This should be a negative value.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -881,17 +915,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>page_five</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Page Five</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Enter the answer</t>
+          <t>This is the fifth page of the assessment.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -908,18 +942,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>page_seven</t>
+          <t>question_eleven</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Page Seven</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Question Eleven</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Use the correct base 10 logarithm.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -931,18 +969,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>question_twelve</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What is the value of log 0?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Question Twelve</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Simplify your answer.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -954,17 +996,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>page_six</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Page Six</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Enter the answer</t>
+          <t>This is the sixth page of the assessment.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -981,18 +1023,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>page_eight</t>
+          <t>question_thirteen</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Page Eight</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Question Thirteen</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Use the correct base 10 logarithm.</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1004,18 +1050,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>question_fourteen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What is the value of log (-1) / 4?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Question Fourteen</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>This should be an undefined value.</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1027,17 +1077,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>page_seven</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Page Seven</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Enter the answer</t>
+          <t>This is the seventh page of the assessment.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1054,18 +1104,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>page_nine</t>
+          <t>question_fifteen</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Page Nine</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Question Fifteen</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Simplify your answer.</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1077,18 +1131,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>question_sixteen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>What is the value of log 2 + 3?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Question Sixteen</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Use the correct base 10 logarithm.</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1100,20 +1158,205 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>question_seventeen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Question Seventeen</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Enter the answer</t>
+          <t>This should be an undefined value.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>page_eight</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Page Eight</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>This is the eighth page of the assessment.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>question_eighteen</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Question Eighteen</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Simplify your answer.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>question_nineteen</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Question Nineteen</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Use the correct base 10 logarithm.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>page_nine</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Page Nine</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>This is the ninth page of the assessment.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>question_twenty</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Question Twenty</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Simplify your answer.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>question_twenty_one</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Question Twenty One</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Use the correct base 10 logarithm.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>page_ten</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Page Ten</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1125,93 +1368,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>list_name</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>logarithm_type_choices</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>natural_logarithm</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Natural Logarithm</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>logarithm_type_choices</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>base-2_logarithm</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Base-2 Logarithm</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>logarithm_type_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>base-10_logarithm</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Base-10 Logarithm</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
